--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484626_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484626_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.671200000000001</v>
+        <v>8.079800000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>9.578799999999999</v>
+        <v>8.383900000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09229999999999999</v>
+        <v>-0.304</v>
       </c>
       <c r="G2" t="n">
         <v>2.9561</v>
@@ -610,13 +610,13 @@
         <v>1.2828</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2727</v>
+        <v>1.6814</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8296</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4431</v>
+        <v>1.0467</v>
       </c>
       <c r="V2" t="n">
         <v>2.3429</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3077</v>
+        <v>1.6974</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5546</v>
+        <v>2.2416</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2469</v>
+        <v>-0.5442</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0718</v>
@@ -766,13 +766,13 @@
         <v>0.5498</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8297</v>
+        <v>1.2194</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4774</v>
+        <v>0.2097</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3071</v>
+        <v>1.0098</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.722</v>
+        <v>0.7934</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3624</v>
+        <v>0.4585</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3596</v>
+        <v>0.3349</v>
       </c>
       <c r="G5" t="n">
         <v>0.2619</v>
@@ -844,13 +844,13 @@
         <v>0.1833</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2768</v>
+        <v>0.3482</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0369</v>
+        <v>0.0592</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3138</v>
+        <v>0.289</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MONFORTE MARTINEZ</t>
+          <t>E. NAVARRO VALDÉS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4114</v>
+        <v>0.3251</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7629</v>
+        <v>0.3251</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.3515</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2765</v>
+        <v>0.3251</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2601</v>
+        <v>0.3251</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0164</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.3251</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8328</v>
+        <v>0.3251</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0417</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.151</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0929</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0581</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3665</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7429</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5377</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2052</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3115</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. NAVARRO VALDÉS</t>
+          <t>D. CHALATASHVILI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3251</v>
+        <v>-0.5795</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3251</v>
+        <v>0.7398</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-1.3193</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3251</v>
+        <v>0.4753</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3251</v>
+        <v>0.5202</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-0.0449</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3251</v>
+        <v>1.8722</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3251</v>
+        <v>1.1796</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.6925</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-1.3968</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.6594</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.1833</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.0995</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.2161</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.4361</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.4581</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.4581</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. CHALATASHVILI</t>
+          <t>J. MONFORTE MARTINEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8159999999999999</v>
+        <v>-0.8226</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4785</v>
+        <v>1.8014</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2945</v>
+        <v>-2.624</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4753</v>
+        <v>-1.2765</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5202</v>
+        <v>-0.2601</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0449</v>
+        <v>-1.0164</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8722</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1796</v>
+        <v>0.8328</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6925</v>
+        <v>0.0417</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3968</v>
+        <v>-2.151</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6594</v>
+        <v>-1.0929</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-1.0581</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1833</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0995</v>
+        <v>0.5498</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0165</v>
+        <v>0.5089</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4774</v>
+        <v>0.5762</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4608</v>
+        <v>-0.0673</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4581</v>
+        <v>0.3115</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4581</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4076</v>
+        <v>-2.2095</v>
       </c>
       <c r="E9" t="n">
         <v>-1.0857</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.322</v>
+        <v>-1.1238</v>
       </c>
       <c r="G9" t="n">
         <v>0.09370000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>0.5498</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3626</v>
+        <v>-0.1644</v>
       </c>
       <c r="T9" t="n">
         <v>-0.1471</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2155</v>
+        <v>-0.0174</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5889</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. SORO VILLANUEVA</t>
+          <t>H. PAMUK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8161</v>
+        <v>-3.425</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7134</v>
+        <v>-1.7913</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.5294</v>
+        <v>-1.6337</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6212</v>
+        <v>-3.7597</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9015</v>
+        <v>-2.7306</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.5227</v>
+        <v>-1.0291</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6289</v>
+        <v>-1.0395</v>
       </c>
       <c r="K10" t="n">
-        <v>2.2601</v>
+        <v>-1.1645</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6312</v>
+        <v>0.125</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.2501</v>
+        <v>-2.7202</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3585</v>
+        <v>-1.5661</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.8916</v>
+        <v>-1.1541</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0158</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9321</v>
+        <v>-0.9163</v>
       </c>
       <c r="R10" t="n">
         <v>0.9163</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4649</v>
+        <v>0.3346</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7496</v>
+        <v>0.1644</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2848</v>
+        <v>0.1702</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.9109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. PAMUK</t>
+          <t>E. NAVARRO VALDES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8454</v>
+        <v>-3.5161</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2861</v>
+        <v>-0.8827</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5594</v>
+        <v>-2.6334</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.7597</v>
+        <v>0.3668</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.7306</v>
+        <v>-0.3321</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0291</v>
+        <v>0.6989</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0395</v>
+        <v>2.6139</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1645</v>
+        <v>0.5044</v>
       </c>
       <c r="L11" t="n">
-        <v>0.125</v>
+        <v>2.1095</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.7202</v>
+        <v>-2.2471</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5661</v>
+        <v>-0.8365</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1541</v>
+        <v>-1.4106</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R11" t="n">
         <v>0.9163</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0858</v>
+        <v>0.6459</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3303</v>
+        <v>0.1686</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2446</v>
+        <v>0.4774</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.78</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. NAVARRO VALDES</t>
+          <t>R. SORO VILLANUEVA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0519</v>
+        <v>-4.052</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4185</v>
+        <v>0.3288</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6334</v>
+        <v>-4.3808</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3668</v>
+        <v>-1.6212</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3321</v>
+        <v>0.9015</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6989</v>
+        <v>-2.5227</v>
       </c>
       <c r="J12" t="n">
-        <v>2.6139</v>
+        <v>1.6289</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5044</v>
+        <v>2.2601</v>
       </c>
       <c r="L12" t="n">
-        <v>2.1095</v>
+        <v>-0.6312</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.2471</v>
+        <v>-3.2501</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8365</v>
+        <v>-1.3585</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.4106</v>
+        <v>-1.8916</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.7489</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.6651</v>
+        <v>-2.9321</v>
       </c>
       <c r="R12" t="n">
         <v>0.9163</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1101</v>
+        <v>0.2289</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3673</v>
+        <v>0.365</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4774</v>
+        <v>-0.1361</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.78</v>
+        <v>-0.6439</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.78</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.4195</v>
+        <v>-4.1275</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.639</v>
+        <v>-1.57</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.7805</v>
+        <v>-2.5575</v>
       </c>
       <c r="G13" t="n">
         <v>-5.0252</v>
@@ -1468,13 +1468,13 @@
         <v>1.8326</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3674</v>
+        <v>0.6593</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4193</v>
+        <v>0.4883</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.052</v>
+        <v>0.171</v>
       </c>
       <c r="V13" t="n">
         <v>0.4216</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. ROMAN MORA</t>
+          <t>E. CIRCUNS RIVERA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.7838</v>
+        <v>-4.9168</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.3569</v>
+        <v>-2.3219</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.4269</v>
+        <v>-2.5949</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.1624</v>
+        <v>-4.65</v>
       </c>
       <c r="H14" t="n">
-        <v>1.104</v>
+        <v>-2.5987</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.2663</v>
+        <v>-2.0513</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6295</v>
+        <v>-1.8501</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4272</v>
+        <v>-1.9789</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2023</v>
+        <v>0.1288</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.7919</v>
+        <v>-2.7999</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.3232</v>
+        <v>-0.6198</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.4686</v>
+        <v>-2.1801</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.7489</v>
+        <v>0.1833</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.7647</v>
+        <v>-0.9163</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0158</v>
+        <v>1.0995</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4145</v>
+        <v>0.4949</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2217</v>
+        <v>0.1226</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1928</v>
+        <v>0.3723</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.4581</v>
+        <v>-0.945</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4581</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. CIRCUNS RIVERA</t>
+          <t>R. ROMAN MORA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.8239</v>
+        <v>-4.9477</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.1051</v>
+        <v>-0.9172</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.7188</v>
+        <v>-4.0305</v>
       </c>
       <c r="G15" t="n">
-        <v>-4.65</v>
+        <v>-1.1624</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.5987</v>
+        <v>1.104</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.0513</v>
+        <v>-2.2663</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.8501</v>
+        <v>3.6295</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.9789</v>
+        <v>3.4272</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1288</v>
+        <v>0.2023</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.7999</v>
+        <v>-4.7919</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6198</v>
+        <v>-2.3232</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.1801</v>
+        <v>-2.4686</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1833</v>
+        <v>-2.7489</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9163</v>
+        <v>-4.7647</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0995</v>
+        <v>2.0158</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4121</v>
+        <v>0.4216</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6606</v>
+        <v>0.218</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2485</v>
+        <v>0.2036</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.945</v>
+        <v>-1.4581</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.267</v>
+        <v>-1.4581</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-15.651</v>
+        <v>-14.8252</v>
       </c>
       <c r="E16" t="n">
-        <v>7.760200000000001</v>
+        <v>8.586100000000002</v>
       </c>
       <c r="F16" t="n">
-        <v>-23.4114</v>
+        <v>-23.4112</v>
       </c>
       <c r="G16" t="n">
         <v>-10.2121</v>
@@ -1672,10 +1672,10 @@
         <v>-1.8772</v>
       </c>
       <c r="I16" t="n">
-        <v>-8.3348</v>
+        <v>-8.334800000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>17.9231</v>
+        <v>17.92310000000001</v>
       </c>
       <c r="K16" t="n">
         <v>10.8687</v>
@@ -1702,13 +1702,13 @@
         <v>11.9118</v>
       </c>
       <c r="S16" t="n">
-        <v>5.773000000000001</v>
+        <v>6.598700000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>1.817499999999999</v>
+        <v>2.6434</v>
       </c>
       <c r="U16" t="n">
-        <v>3.9554</v>
+        <v>3.955299999999999</v>
       </c>
       <c r="V16" t="n">
         <v>-4.798</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>9.167899999999999</v>
+        <v>10.1222</v>
       </c>
       <c r="E17" t="n">
-        <v>8.738799999999999</v>
+        <v>9.411899999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4291</v>
+        <v>0.7103</v>
       </c>
       <c r="G17" t="n">
         <v>5.2822</v>
@@ -1780,13 +1780,13 @@
         <v>3.4819</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.8523</v>
+        <v>-0.898</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4132</v>
+        <v>-0.7402</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.439</v>
+        <v>-0.1578</v>
       </c>
       <c r="V17" t="n">
         <v>4.4552</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>6.4323</v>
+        <v>7.2365</v>
       </c>
       <c r="E18" t="n">
-        <v>6.9728</v>
+        <v>7.5497</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5405</v>
+        <v>-0.3132</v>
       </c>
       <c r="G18" t="n">
         <v>5.1648</v>
@@ -1858,13 +1858,13 @@
         <v>2.7489</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3268</v>
+        <v>-0.5226</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0829</v>
+        <v>-0.506</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2439</v>
+        <v>-0.0166</v>
       </c>
       <c r="V18" t="n">
         <v>0.945</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5397</v>
+        <v>1.6636</v>
       </c>
       <c r="E19" t="n">
         <v>2.6347</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.095</v>
+        <v>-0.9711</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1054</v>
@@ -1936,13 +1936,13 @@
         <v>0.733</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7055</v>
+        <v>-0.5816</v>
       </c>
       <c r="T19" t="n">
         <v>-0.5324</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1731</v>
+        <v>-0.0492</v>
       </c>
       <c r="V19" t="n">
         <v>2.5339</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. FOS CERVERA</t>
+          <t>S. ARNAIZ VEGA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6204</v>
+        <v>0.8803</v>
       </c>
       <c r="E20" t="n">
-        <v>5.4036</v>
+        <v>0.707</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.7832</v>
+        <v>0.1734</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7748</v>
+        <v>2.3283</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2814</v>
+        <v>1.9466</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4934</v>
+        <v>0.3817</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5869</v>
+        <v>3.8734</v>
       </c>
       <c r="K20" t="n">
-        <v>2.0032</v>
+        <v>2.9786</v>
       </c>
       <c r="L20" t="n">
-        <v>1.5836</v>
+        <v>0.8949</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.8121</v>
+        <v>-1.5451</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7219</v>
+        <v>-1.032</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0902</v>
+        <v>-0.5131</v>
       </c>
       <c r="P20" t="n">
-        <v>2.0158</v>
+        <v>0.3665</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.3665</v>
+        <v>-2.1991</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3823</v>
+        <v>2.5656</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2698</v>
+        <v>-0.8799</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0392</v>
+        <v>-0.6663</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2306</v>
+        <v>-0.2136</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.9005</v>
+        <v>-0.9346</v>
       </c>
       <c r="W20" t="n">
-        <v>2.2224</v>
+        <v>-0.3011</v>
       </c>
       <c r="X20" t="n">
-        <v>-4.1229</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. ARNAIZ VEGA</t>
+          <t>B. FOS CERVERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5962</v>
+        <v>0.4179</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8031</v>
+        <v>5.0189</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2069</v>
+        <v>-4.6011</v>
       </c>
       <c r="G21" t="n">
-        <v>2.3283</v>
+        <v>0.7748</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9466</v>
+        <v>0.2814</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3817</v>
+        <v>0.4934</v>
       </c>
       <c r="J21" t="n">
-        <v>3.8734</v>
+        <v>3.5869</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9786</v>
+        <v>2.0032</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8949</v>
+        <v>1.5836</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5451</v>
+        <v>-2.8121</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.032</v>
+        <v>-1.7219</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5131</v>
+        <v>-1.0902</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3665</v>
+        <v>2.0158</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1991</v>
+        <v>-0.3665</v>
       </c>
       <c r="R21" t="n">
-        <v>2.5656</v>
+        <v>2.3823</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.164</v>
+        <v>-0.4723</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-0.4238</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5939</v>
+        <v>-0.0485</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9346</v>
+        <v>-1.9005</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3011</v>
+        <v>2.2224</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6335</v>
+        <v>-4.1229</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1178</v>
+        <v>0.3174</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9815</v>
+        <v>1.0777</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8637</v>
+        <v>-0.7603</v>
       </c>
       <c r="G22" t="n">
         <v>0.1524</v>
@@ -2170,13 +2170,13 @@
         <v>1.0995</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9509</v>
+        <v>-0.7513</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.6746</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1802</v>
+        <v>-0.0767</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. MONTILLA GONZALEZ</t>
+          <t>M. ANTONI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4084</v>
+        <v>-0.9182</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4793</v>
+        <v>0.4523</v>
       </c>
       <c r="F23" t="n">
-        <v>1.071</v>
+        <v>-1.3704</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.4492</v>
+        <v>1.0641</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.9873</v>
+        <v>1.0418</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4619</v>
+        <v>0.0223</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.6279</v>
+        <v>3.0335</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.128</v>
+        <v>2.2417</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5001</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.8213</v>
+        <v>-1.9694</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.8593</v>
+        <v>-1.1999</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.962</v>
+        <v>-0.7695</v>
       </c>
       <c r="P23" t="n">
         <v>0.1833</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.1154</v>
+        <v>-1.8326</v>
       </c>
       <c r="R23" t="n">
-        <v>3.2986</v>
+        <v>2.0158</v>
       </c>
       <c r="S23" t="n">
-        <v>1.2686</v>
+        <v>-0.2754</v>
       </c>
       <c r="T23" t="n">
-        <v>0.675</v>
+        <v>-0.1255</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5936</v>
+        <v>-0.1499</v>
       </c>
       <c r="V23" t="n">
-        <v>1.5889</v>
+        <v>-1.89</v>
       </c>
       <c r="W23" t="n">
-        <v>1.5889</v>
+        <v>-0.6231</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. ANTONI RODRIGUEZ</t>
+          <t>J. MONTILLA GONZALEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.415</v>
+        <v>-2.7867</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3561</v>
+        <v>-3.4409</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7711</v>
+        <v>0.6542</v>
       </c>
       <c r="G24" t="n">
-        <v>1.0641</v>
+        <v>-4.4492</v>
       </c>
       <c r="H24" t="n">
-        <v>1.0418</v>
+        <v>-3.9873</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0223</v>
+        <v>-0.4619</v>
       </c>
       <c r="J24" t="n">
-        <v>3.0335</v>
+        <v>-1.6279</v>
       </c>
       <c r="K24" t="n">
-        <v>2.2417</v>
+        <v>-2.128</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.5001</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.9694</v>
+        <v>-2.8213</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1999</v>
+        <v>-1.8593</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7695</v>
+        <v>-0.962</v>
       </c>
       <c r="P24" t="n">
         <v>0.1833</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.8326</v>
+        <v>-3.1154</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0158</v>
+        <v>3.2986</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7723</v>
+        <v>-0.1097</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2217</v>
+        <v>-0.2865</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5506</v>
+        <v>0.1768</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.89</v>
+        <v>1.5889</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.6231</v>
+        <v>1.5889</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>15.6509</v>
+        <v>16.933</v>
       </c>
       <c r="E25" t="n">
         <v>23.4113</v>
       </c>
       <c r="F25" t="n">
-        <v>-7.760299999999999</v>
+        <v>-6.478199999999999</v>
       </c>
       <c r="G25" t="n">
         <v>10.212</v>
@@ -2374,7 +2374,7 @@
         <v>1.877</v>
       </c>
       <c r="I25" t="n">
-        <v>8.334800000000001</v>
+        <v>8.3348</v>
       </c>
       <c r="J25" t="n">
         <v>28.1351</v>
@@ -2404,22 +2404,22 @@
         <v>18.3256</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.773</v>
+        <v>-4.4908</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.9552</v>
+        <v>-3.9553</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.8177</v>
+        <v>-0.5355000000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>4.7979</v>
+        <v>4.797899999999999</v>
       </c>
       <c r="W25" t="n">
         <v>11.1432</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.3453</v>
+        <v>-6.345299999999999</v>
       </c>
     </row>
   </sheetData>
